--- a/Financial-Analytics_Follow-Along-Solution.xlsx
+++ b/Financial-Analytics_Follow-Along-Solution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\plumsolutions-meetup-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251ABA1E-D6C8-4D82-9649-A178231F8685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C879C61F-79C9-459D-8B15-27952AC88CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="13">
+  <futureMetadata name="XLRICHVALUE" count="16">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -68,6 +68,27 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="21"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="23"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="24"/>
         </ext>
       </extLst>
@@ -75,7 +96,49 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="25"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="26"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="27"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="28"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="29"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="30"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="34"/>
         </ext>
       </extLst>
     </bk>
@@ -96,49 +159,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="47"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="50"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="53"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="56"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="59"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="63"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="66"/>
+          <xlrd:rvb i="45"/>
         </ext>
       </extLst>
     </bk>
@@ -148,7 +169,7 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="13">
+  <valueMetadata count="16">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -187,6 +208,15 @@
     </bk>
     <bk>
       <rc t="2" v="12"/>
+    </bk>
+    <bk>
+      <rc t="2" v="13"/>
+    </bk>
+    <bk>
+      <rc t="2" v="14"/>
+    </bk>
+    <bk>
+      <rc t="2" v="15"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -242,7 +272,7 @@
     seasonal_periods=12,
 ).fit()
 forecast = fit.forecast(12)
-forecast</code>
+forecast.head(8)</code>
     </pythonScript>
     <pythonScript>
       <code>train = df[df.index &lt; '2024-01-01']
@@ -762,13 +792,21 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -776,8 +814,7 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -789,13 +826,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -812,6 +842,158 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>209551</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>42008</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Image generated by Python">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DAB96CA-D6BC-D301-1579-AB48B97B226B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="'follow-along'!E30"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6962776" y="9315450"/>
+          <a:ext cx="3157538" cy="2351821"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>319087</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>108481</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="Image generated by Python">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{065CF598-71C5-0706-C707-7F9649108FDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="'follow-along'!E41"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6962775" y="12168189"/>
+          <a:ext cx="3267075" cy="2437342"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>119063</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>155883</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3" descr="Image generated by Python">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86B17891-D8E3-8E59-93F0-0D05215FE9EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="'follow-along'!E118"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6962776" y="37247514"/>
+          <a:ext cx="2419350" cy="1722744"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -855,7 +1037,7 @@
 </file>
 
 <file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="12">
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="5">
   <a r="7" c="2">
     <v t="s"/>
     <v t="s">revenue</v>
@@ -914,57 +1096,23 @@
     <v>345083.33333333331</v>
   </a>
   <a r="2">
-    <v>580</v>
-    <v>432</v>
-  </a>
-  <a r="2">
     <v>630</v>
     <v>470</v>
   </a>
   <a r="11" c="2">
-    <v t="r">29</v>
-    <v>346778.31609928777</v>
-    <v t="r">30</v>
-    <v>341924.58560126484</v>
-    <v t="r">31</v>
-    <v>375989.75822129659</v>
-    <v t="r">32</v>
-    <v>383916.0444150705</v>
-    <v t="r">33</v>
-    <v>401409.17151548882</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="r">34</v>
-    <v>374561.47907110606</v>
-    <v t="r">35</v>
-    <v>420312.08873984846</v>
-    <v t="r">36</v>
-    <v>427432.06128523842</v>
-    <v t="r">37</v>
-    <v>449599.47849625314</v>
-    <v t="r">38</v>
-    <v>462825.8166091473</v>
-  </a>
-  <a r="2" c="2">
-    <v t="s">Holt-Winters MAE</v>
-    <v>17552</v>
-    <v t="s">Baseline MAE</v>
-    <v>41983</v>
-  </a>
-  <a r="11" c="2">
-    <v t="r">29</v>
+    <v t="r">23</v>
     <v>118.99805092732569</v>
-    <v t="r">30</v>
+    <v t="r">24</v>
     <v>120.10606432601419</v>
-    <v t="r">31</v>
+    <v t="r">25</v>
     <v>121.2140777247027</v>
-    <v t="r">32</v>
+    <v t="r">26</v>
     <v>122.3220911233912</v>
-    <v t="r">33</v>
+    <v t="r">27</v>
     <v>123.43010452207972</v>
     <v t="s">...</v>
     <v t="s">...</v>
-    <v t="r">34</v>
+    <v t="r">30</v>
     <v>126.75414471814523</v>
     <v t="r">35</v>
     <v>127.86215811683374</v>
@@ -974,42 +1122,6 @@
     <v>130.07818491421077</v>
     <v t="r">38</v>
     <v>131.18619831289925</v>
-  </a>
-  <a r="8" c="2">
-    <v t="s">count</v>
-    <v>10000</v>
-    <v t="s">mean</v>
-    <v>999.57280332631467</v>
-    <v t="s">std</v>
-    <v>200.69247610068081</v>
-    <v t="s">min</v>
-    <v>215.51994967633152</v>
-    <v t="s">25%</v>
-    <v>865.48189399857949</v>
-    <v t="s">50%</v>
-    <v>999.48100484142446</v>
-    <v t="s">75%</v>
-    <v>1134.216177572933</v>
-    <v t="s">max</v>
-    <v>1785.2475412872654</v>
-  </a>
-  <a r="8" c="2">
-    <v t="s">count</v>
-    <v>10000</v>
-    <v t="s">mean</v>
-    <v>14998.252053092408</v>
-    <v t="s">std</v>
-    <v>7463.739795284424</v>
-    <v t="s">min</v>
-    <v>-22224.002516183424</v>
-    <v t="s">25%</v>
-    <v>10274.094699928975</v>
-    <v t="s">50%</v>
-    <v>16974.050242071222</v>
-    <v t="s">75%</v>
-    <v>22000</v>
-    <v t="s">max</v>
-    <v>22000</v>
   </a>
   <a r="2" c="5">
     <v t="s"/>
@@ -1023,37 +1135,11 @@
     <v>22000</v>
     <v>4.5999999999999999E-2</v>
   </a>
-  <a r="2">
-    <v>580</v>
-    <v>413</v>
-  </a>
-  <a r="4" c="5">
-    <v t="s"/>
-    <v t="s">inventory</v>
-    <v t="s">mean</v>
-    <v t="s">p10</v>
-    <v t="s">prob_loss</v>
-    <v>0</v>
-    <v>900</v>
-    <v>16007</v>
-    <v>10077</v>
-    <v>1.0999999999999999E-2</v>
-    <v>1</v>
-    <v>1100</v>
-    <v>14998</v>
-    <v>4077</v>
-    <v>4.5999999999999999E-2</v>
-    <v>2</v>
-    <v>1300</v>
-    <v>10681</v>
-    <v>-1923</v>
-    <v>0.13500000000000001</v>
-  </a>
 </arrayData>
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="67">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="46">
   <rv s="0">
     <fb>43466</fb>
     <v>2</v>
@@ -1160,66 +1246,64 @@
   <rv s="4">
     <v>0</v>
     <v>9</v>
+    <v>Image generated by Python</v>
+  </rv>
+  <rv s="4">
+    <v>1</v>
+    <v>9</v>
+    <v>Image generated by Python</v>
+  </rv>
+  <rv s="0">
+    <fb>45658</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>45689</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>45717</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>45748</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>45778</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>45809</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>45839</fb>
+    <v>2</v>
+  </rv>
+  <rv s="0">
+    <fb>45870</fb>
+    <v>2</v>
+  </rv>
+  <rv s="5">
+    <v>2</v>
+    <v>9</v>
   </rv>
   <rv s="1">
     <v>2</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>Image</v>
     <v>6</v>
-    <v>21</v>
-    <v>22</v>
+    <v>31</v>
+    <v>32</v>
   </rv>
   <rv s="3">
     <v>&lt;class 'PIL.PngImagePlugin.PngImageFile'&gt;</v>
     <v>PngImageFile</v>
-    <v>&lt;PIL.PngImagePlugin.PngImageFile image mode=RGBA size=580x432 at 0x7F22A09B2DB0&gt;</v>
-    <v>23</v>
+    <v>&lt;PIL.PngImagePlugin.PngImageFile image mode=RGBA size=630x470 at 0x7EFD482750A0&gt;</v>
+    <v>33</v>
     <v>3</v>
-  </rv>
-  <rv s="4">
-    <v>1</v>
-    <v>9</v>
-  </rv>
-  <rv s="1">
-    <v>3</v>
-  </rv>
-  <rv s="5">
-    <v>Image</v>
-    <v>6</v>
-    <v>25</v>
-    <v>26</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'PIL.PngImagePlugin.PngImageFile'&gt;</v>
-    <v>PngImageFile</v>
-    <v>&lt;PIL.PngImagePlugin.PngImageFile image mode=RGBA size=630x470 at 0x7F2296F40B30&gt;</v>
-    <v>27</v>
-    <v>3</v>
-  </rv>
-  <rv s="0">
-    <fb>45658</fb>
-    <v>2</v>
-  </rv>
-  <rv s="0">
-    <fb>45689</fb>
-    <v>2</v>
-  </rv>
-  <rv s="0">
-    <fb>45717</fb>
-    <v>2</v>
-  </rv>
-  <rv s="0">
-    <fb>45748</fb>
-    <v>2</v>
-  </rv>
-  <rv s="0">
-    <fb>45778</fb>
-    <v>2</v>
-  </rv>
-  <rv s="0">
-    <fb>45870</fb>
-    <v>2</v>
   </rv>
   <rv s="0">
     <fb>45901</fb>
@@ -1238,70 +1322,12 @@
     <v>2</v>
   </rv>
   <rv s="1">
-    <v>4</v>
+    <v>3</v>
   </rv>
   <rv s="2">
     <v>Series</v>
     <v>8</v>
     <v>39</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'pandas.core.series.Series'&gt;</v>
-    <v>Series</v>
-    <v>2025-01-01    346778.316099
-2025-02-01    341924.585601
-2025-03-01    375989.758221
-2025-04-01    383916.044415
-2025-05-01    401409.171515
-2025-06-01    381123.992333
-2025-07-01    361825.033115
-2025-08-01    374561.479071
-2025-09-01    420312.088740
-...</v>
-    <v>40</v>
-    <v>3</v>
-  </rv>
-  <rv s="1">
-    <v>5</v>
-  </rv>
-  <rv s="2">
-    <v>Series</v>
-    <v>10</v>
-    <v>42</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'pandas.core.series.Series'&gt;</v>
-    <v>Series</v>
-    <v>Holt-Winters MAE    17552
-Baseline MAE        41983
-dtype: int64</v>
-    <v>43</v>
-    <v>3</v>
-  </rv>
-  <rv s="4">
-    <v>2</v>
-    <v>9</v>
-  </rv>
-  <rv s="5">
-    <v>Image</v>
-    <v>6</v>
-    <v>45</v>
-    <v>26</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'PIL.PngImagePlugin.PngImageFile'&gt;</v>
-    <v>PngImageFile</v>
-    <v>&lt;PIL.PngImagePlugin.PngImageFile image mode=RGBA size=630x470 at 0x7F229863A480&gt;</v>
-    <v>46</v>
-    <v>3</v>
-  </rv>
-  <rv s="1">
-    <v>6</v>
-  </rv>
-  <rv s="2">
-    <v>Series</v>
-    <v>8</v>
-    <v>48</v>
   </rv>
   <rv s="3">
     <v>&lt;class 'pandas.core.series.Series'&gt;</v>
@@ -1317,114 +1343,35 @@
 2025-09-01    127.862158
 2025-10-01    128.970172
 20...</v>
-    <v>49</v>
+    <v>40</v>
     <v>3</v>
   </rv>
   <rv s="1">
-    <v>7</v>
-  </rv>
-  <rv s="2">
-    <v>Series</v>
-    <v>12</v>
-    <v>51</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'pandas.core.series.Series'&gt;</v>
-    <v>Series</v>
-    <v>count    10000.000000
-mean       999.572803
-std        200.692476
-min        215.519950
-25%        865.481894
-50%        999.481005
-75%       1134.216178
-max       1785.247541
-dtype: float64</v>
-    <v>52</v>
-    <v>3</v>
-  </rv>
-  <rv s="1">
-    <v>8</v>
-  </rv>
-  <rv s="2">
-    <v>Series</v>
-    <v>12</v>
-    <v>54</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'pandas.core.series.Series'&gt;</v>
-    <v>Series</v>
-    <v>count    10000.000000
-mean     14998.252053
-std       7463.739795
-min     -22224.002516
-25%      10274.094700
-50%      16974.050242
-75%      22000.000000
-max      22000.000000
-dtype: float64</v>
-    <v>55</v>
-    <v>3</v>
-  </rv>
-  <rv s="1">
-    <v>9</v>
+    <v>4</v>
   </rv>
   <rv s="2">
     <v>DataFrame</v>
-    <v>14</v>
-    <v>57</v>
+    <v>10</v>
+    <v>42</v>
   </rv>
   <rv s="3">
     <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
     <v>DataFrame</v>
     <v xml:space="preserve">    mean   p10    p90  prob_loss
 0  14998  4077  22000      0.046</v>
-    <v>58</v>
+    <v>43</v>
     <v>3</v>
   </rv>
   <rv s="4">
     <v>3</v>
     <v>9</v>
-  </rv>
-  <rv s="1">
-    <v>10</v>
-  </rv>
-  <rv s="5">
-    <v>Image</v>
-    <v>6</v>
-    <v>60</v>
-    <v>61</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'PIL.PngImagePlugin.PngImageFile'&gt;</v>
-    <v>PngImageFile</v>
-    <v>&lt;PIL.PngImagePlugin.PngImageFile image mode=RGBA size=580x413 at 0x7F22966FD400&gt;</v>
-    <v>62</v>
-    <v>3</v>
-  </rv>
-  <rv s="1">
-    <v>11</v>
-  </rv>
-  <rv s="2">
-    <v>DataFrame</v>
-    <v>16</v>
-    <v>64</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
-    <v>DataFrame</v>
-    <v xml:space="preserve">   inventory   mean    p10  prob_loss
-0        900  16007  10077      0.011
-1       1100  14998   4077      0.046
-2       1300  10681  -1923      0.135</v>
-    <v>65</v>
-    <v>3</v>
+    <v>Image generated by Python</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_formattednumber">
     <k n="_Format" t="spb"/>
   </s>
@@ -1446,6 +1393,11 @@
   <s t="_localImage">
     <k n="_rvRel:LocalImageIdentifier" t="i"/>
     <k n="CalcOrigin" t="i"/>
+    <k n="Text" t="s"/>
+  </s>
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
   </s>
   <s t="_entity">
     <k n="_DisplayString" t="s"/>
@@ -1458,7 +1410,7 @@
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="17">
+  <spbData count="11">
     <spb s="0">
       <v>5</v>
       <v>1</v>
@@ -1499,24 +1451,6 @@
     <spb s="1">
       <v>7</v>
     </spb>
-    <spb s="5">
-      <v>2</v>
-      <v>1</v>
-      <v>Series</v>
-      <v>arrayPreview</v>
-    </spb>
-    <spb s="1">
-      <v>9</v>
-    </spb>
-    <spb s="5">
-      <v>8</v>
-      <v>1</v>
-      <v>Series</v>
-      <v>arrayPreview</v>
-    </spb>
-    <spb s="1">
-      <v>11</v>
-    </spb>
     <spb s="0">
       <v>1</v>
       <v>4</v>
@@ -1525,17 +1459,7 @@
       <v>1</v>
     </spb>
     <spb s="1">
-      <v>13</v>
-    </spb>
-    <spb s="0">
-      <v>3</v>
-      <v>4</v>
-      <v>DataFrame</v>
-      <v>arrayPreview</v>
-      <v>1</v>
-    </spb>
-    <spb s="1">
-      <v>15</v>
+      <v>9</v>
     </spb>
   </spbData>
 </supportingPropertyBags>
@@ -1922,14 +1846,14 @@
   <sheetPr>
     <tabColor rgb="FFCF3338"/>
   </sheetPr>
-  <dimension ref="B1:E135"/>
+  <dimension ref="B1:H135"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.46484375" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="78" customWidth="1"/>
     <col min="4" max="4" width="2" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="5" max="5" width="23.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -1938,13 +1862,13 @@
       </c>
     </row>
     <row r="2" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="19" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="10"/>
     </row>
     <row r="3" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="10"/>
@@ -1955,43 +1879,43 @@
       </c>
     </row>
     <row r="6" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="21"/>
+      <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="21"/>
+      <c r="C7" s="15"/>
     </row>
     <row r="9" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="18"/>
+      <c r="C9" s="21"/>
     </row>
     <row r="10" spans="2:5" ht="56" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="18"/>
+      <c r="C10" s="21"/>
     </row>
     <row r="12" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="15"/>
+      <c r="C12" s="12"/>
     </row>
     <row r="14" spans="2:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="13"/>
+      <c r="C14" s="17"/>
     </row>
     <row r="15" spans="2:5" ht="33" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="10"/>
@@ -2009,19 +1933,19 @@
       </c>
     </row>
     <row r="17" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="10"/>
     </row>
     <row r="26" spans="2:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="13"/>
+      <c r="C26" s="17"/>
     </row>
     <row r="27" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="10"/>
@@ -2039,7 +1963,7 @@
       </c>
     </row>
     <row r="29" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="10"/>
@@ -2052,18 +1976,18 @@
         <v>19</v>
       </c>
       <c r="E30" t="e" cm="1" vm="3">
-        <f t="array" ref="E30">_xlfn._xlws.PY(2,1)</f>
+        <f t="array" ref="E30">_xlfn._xlws.PY(2,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="13"/>
+      <c r="C39" s="17"/>
     </row>
     <row r="40" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C40" s="10"/>
@@ -2076,192 +2000,372 @@
         <v>22</v>
       </c>
       <c r="E41" t="e" cm="1" vm="4">
-        <f t="array" ref="E41">_xlfn._xlws.PY(3,1)</f>
+        <f t="array" ref="E41">_xlfn._xlws.PY(3,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C42" s="10"/>
     </row>
-    <row r="51" spans="2:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B51" s="12" t="s">
+    <row r="51" spans="2:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B51" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C51" s="13"/>
-    </row>
-    <row r="52" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B52" s="16" t="s">
+      <c r="C51" s="17"/>
+    </row>
+    <row r="52" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B52" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C52" s="10"/>
     </row>
-    <row r="53" spans="2:5" ht="173" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:6" ht="173" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B53" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E53" t="e" cm="1" vm="5">
-        <f t="array" ref="E53">_xlfn._xlws.PY(4,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B54" s="11" t="s">
+      <c r="E53" cm="1" vm="5">
+        <f t="array" ref="E53:F60">_xlfn._xlws.PY(4,0)</f>
+        <v>45658</v>
+      </c>
+      <c r="F53">
+        <v>346778.31609928777</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B54" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C54" s="10"/>
-    </row>
-    <row r="63" spans="2:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B63" s="12" t="s">
+      <c r="E54" vm="6">
+        <v>45689</v>
+      </c>
+      <c r="F54">
+        <v>341924.58560126484</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E55" vm="7">
+        <v>45717</v>
+      </c>
+      <c r="F55">
+        <v>375989.75822129659</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E56" vm="8">
+        <v>45748</v>
+      </c>
+      <c r="F56">
+        <v>383916.0444150705</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E57" vm="9">
+        <v>45778</v>
+      </c>
+      <c r="F57">
+        <v>401409.17151548882</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E58" vm="10">
+        <v>45809</v>
+      </c>
+      <c r="F58">
+        <v>381123.99233250675</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E59" vm="11">
+        <v>45839</v>
+      </c>
+      <c r="F59">
+        <v>361825.03311526432</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E60" vm="12">
+        <v>45870</v>
+      </c>
+      <c r="F60">
+        <v>374561.47907110606</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B63" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C63" s="13"/>
-    </row>
-    <row r="64" spans="2:5" ht="33" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B64" s="16" t="s">
+      <c r="C63" s="17"/>
+    </row>
+    <row r="64" spans="2:6" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B64" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C64" s="10"/>
     </row>
-    <row r="65" spans="2:5" ht="188" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:6" ht="188" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B65" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E65" t="e" cm="1" vm="6">
-        <f t="array" ref="E65">_xlfn._xlws.PY(5,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B66" s="11" t="s">
+      <c r="E65" t="str" cm="1">
+        <f t="array" ref="E65:F66">_xlfn._xlws.PY(5,0)</f>
+        <v>Holt-Winters MAE</v>
+      </c>
+      <c r="F65">
+        <v>17552</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B66" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C66" s="10"/>
-    </row>
-    <row r="75" spans="2:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B75" s="12" t="s">
+      <c r="E66" t="str">
+        <v>Baseline MAE</v>
+      </c>
+      <c r="F66">
+        <v>41983</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B75" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C75" s="13"/>
-    </row>
-    <row r="76" spans="2:5" ht="33" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B76" s="16" t="s">
+      <c r="C75" s="17"/>
+    </row>
+    <row r="76" spans="2:6" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B76" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C76" s="10"/>
     </row>
-    <row r="77" spans="2:5" ht="83" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:6" ht="83" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B77" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E77" t="e" cm="1" vm="7">
+      <c r="E77" t="e" cm="1" vm="13">
         <f t="array" ref="E77">_xlfn._xlws.PY(6,1,bookings[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="78" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B78" s="11" t="s">
+    <row r="78" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B78" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C78" s="10"/>
     </row>
-    <row r="79" spans="2:5" ht="23" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:6" ht="23" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B79" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E79" t="e" cm="1" vm="8">
+      <c r="E79" t="e" cm="1" vm="14">
         <f t="array" ref="E79">_xlfn._xlws.PY(7,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="88" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B88" s="14" t="s">
+    <row r="88" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B88" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C88" s="15"/>
-    </row>
-    <row r="90" spans="2:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B90" s="12" t="s">
+      <c r="C88" s="12"/>
+    </row>
+    <row r="90" spans="2:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B90" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C90" s="13"/>
-    </row>
-    <row r="91" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B91" s="16" t="s">
+      <c r="C90" s="17"/>
+    </row>
+    <row r="91" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B91" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C91" s="10"/>
     </row>
-    <row r="92" spans="2:5" ht="68" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:6" ht="68" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B92" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E92" t="e" cm="1" vm="9">
-        <f t="array" ref="E92">_xlfn._xlws.PY(8,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B93" s="11" t="s">
+      <c r="E92" t="str" cm="1">
+        <f t="array" ref="E92:F99">_xlfn._xlws.PY(8,0)</f>
+        <v>count</v>
+      </c>
+      <c r="F92">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B93" s="13" t="s">
         <v>41</v>
       </c>
       <c r="C93" s="10"/>
-    </row>
-    <row r="102" spans="2:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B102" s="12" t="s">
+      <c r="E93" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F93">
+        <v>999.57280332631467</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E94" t="str">
+        <v>std</v>
+      </c>
+      <c r="F94">
+        <v>200.69247610068081</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E95" t="str">
+        <v>min</v>
+      </c>
+      <c r="F95">
+        <v>215.51994967633152</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E96" t="str">
+        <v>25%</v>
+      </c>
+      <c r="F96">
+        <v>865.48189399857949</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E97" t="str">
+        <v>50%</v>
+      </c>
+      <c r="F97">
+        <v>999.48100484142446</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E98" t="str">
+        <v>75%</v>
+      </c>
+      <c r="F98">
+        <v>1134.216177572933</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E99" t="str">
+        <v>max</v>
+      </c>
+      <c r="F99">
+        <v>1785.2475412872654</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B102" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C102" s="13"/>
-    </row>
-    <row r="103" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B103" s="16" t="s">
+      <c r="C102" s="17"/>
+    </row>
+    <row r="103" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B103" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C103" s="10"/>
     </row>
-    <row r="104" spans="2:5" ht="83" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:6" ht="83" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B104" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E104" t="e" cm="1" vm="10">
-        <f t="array" ref="E104">_xlfn._xlws.PY(9,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="105" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B105" s="11" t="s">
+      <c r="E104" t="str" cm="1">
+        <f t="array" ref="E104:F111">_xlfn._xlws.PY(9,0)</f>
+        <v>count</v>
+      </c>
+      <c r="F104">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B105" s="13" t="s">
         <v>45</v>
       </c>
       <c r="C105" s="10"/>
+      <c r="E105" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F105">
+        <v>14998.252053092408</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E106" t="str">
+        <v>std</v>
+      </c>
+      <c r="F106">
+        <v>7463.739795284424</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E107" t="str">
+        <v>min</v>
+      </c>
+      <c r="F107">
+        <v>-22224.002516183424</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E108" t="str">
+        <v>25%</v>
+      </c>
+      <c r="F108">
+        <v>10274.094699928975</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E109" t="str">
+        <v>50%</v>
+      </c>
+      <c r="F109">
+        <v>16974.050242071222</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E110" t="str">
+        <v>75%</v>
+      </c>
+      <c r="F110">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="E111" t="str">
+        <v>max</v>
+      </c>
+      <c r="F111">
+        <v>22000</v>
+      </c>
     </row>
     <row r="114" spans="2:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C114" s="13"/>
+      <c r="C114" s="17"/>
     </row>
     <row r="115" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B115" s="16" t="s">
+      <c r="B115" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C115" s="10"/>
@@ -2273,13 +2377,13 @@
       <c r="C116" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E116" t="e" cm="1" vm="11">
+      <c r="E116" t="e" cm="1" vm="15">
         <f t="array" ref="E116">_xlfn._xlws.PY(10,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="117" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="13" t="s">
         <v>49</v>
       </c>
       <c r="C117" s="10"/>
@@ -2291,63 +2395,120 @@
       <c r="C118" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E118" t="e" cm="1" vm="12">
-        <f t="array" ref="E118">_xlfn._xlws.PY(11,1)</f>
+      <c r="E118" t="e" cm="1" vm="16">
+        <f t="array" ref="E118">_xlfn._xlws.PY(11,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="127" spans="2:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B127" s="12" t="s">
+      <c r="B127" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C127" s="13"/>
+      <c r="C127" s="17"/>
     </row>
     <row r="128" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B128" s="16" t="s">
+      <c r="B128" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C128" s="10"/>
     </row>
-    <row r="129" spans="2:5" ht="158" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:8" ht="158" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B129" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E129" t="e" cm="1" vm="13">
-        <f t="array" ref="E129">_xlfn._xlws.PY(12,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="130" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B130" s="11" t="s">
+      <c r="E129" t="str" cm="1">
+        <f t="array" ref="E129:H132">_xlfn._xlws.PY(12,0)</f>
+        <v>inventory</v>
+      </c>
+      <c r="F129" t="str">
+        <v>mean</v>
+      </c>
+      <c r="G129" t="str">
+        <v>p10</v>
+      </c>
+      <c r="H129" t="str">
+        <v>prob_loss</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B130" s="13" t="s">
         <v>54</v>
       </c>
       <c r="C130" s="10"/>
-    </row>
-    <row r="134" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B134" s="14" t="s">
+      <c r="E130">
+        <v>900</v>
+      </c>
+      <c r="F130">
+        <v>16007</v>
+      </c>
+      <c r="G130">
+        <v>10077</v>
+      </c>
+      <c r="H130">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="E131">
+        <v>1100</v>
+      </c>
+      <c r="F131">
+        <v>14998</v>
+      </c>
+      <c r="G131">
+        <v>4077</v>
+      </c>
+      <c r="H131">
+        <v>4.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="E132">
+        <v>1300</v>
+      </c>
+      <c r="F132">
+        <v>10681</v>
+      </c>
+      <c r="G132">
+        <v>-1923</v>
+      </c>
+      <c r="H132">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="134" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B134" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C134" s="15"/>
-    </row>
-    <row r="135" spans="2:5" ht="38" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B135" s="22" t="s">
+      <c r="C134" s="12"/>
+    </row>
+    <row r="135" spans="2:8" ht="38" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B135" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C135" s="15"/>
+      <c r="C135" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B134:C134"/>
     <mergeCell ref="B115:C115"/>
@@ -2364,24 +2525,17 @@
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B75:C75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
